--- a/tame_output/ON/bt/strategyON_20231212.xlsx
+++ b/tame_output/ON/bt/strategyON_20231212.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-85.8%</t>
+          <t>-85.9%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -42013,7 +42013,7 @@
         <v>45223</v>
       </c>
       <c r="B1761" t="n">
-        <v>3.046980105223825</v>
+        <v>3.046980105223824</v>
       </c>
       <c r="C1761" t="n">
         <v>3.010249418375564</v>
@@ -42036,7 +42036,7 @@
         <v>45224</v>
       </c>
       <c r="B1762" t="n">
-        <v>3.070330524157812</v>
+        <v>3.070330524157811</v>
       </c>
       <c r="C1762" t="n">
         <v>3.010722978056604</v>
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336375</v>
+        <v>3.050895742336374</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42082,7 +42082,7 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320088</v>
+        <v>3.049222094320087</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477762</v>
+        <v>3.055423383477761</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571591</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968025</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -43123,16 +43123,16 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>0.5659653316707827</v>
+        <v>0.5654733158280743</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.335283915075875</v>
+        <v>3.335087108738791</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.799280373182236</v>
+        <v>1.798788357339528</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.188822430630652</v>
+        <v>4.188527221125027</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231212.xlsx
+++ b/tame_output/ON/bt/strategyON_20231212.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-85.9%</t>
+          <t>-86.0%</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.0%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-29.5%</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -42013,7 +42013,7 @@
         <v>45223</v>
       </c>
       <c r="B1761" t="n">
-        <v>3.046980105223824</v>
+        <v>3.046980105223825</v>
       </c>
       <c r="C1761" t="n">
         <v>3.010249418375564</v>
@@ -42036,7 +42036,7 @@
         <v>45224</v>
       </c>
       <c r="B1762" t="n">
-        <v>3.070330524157811</v>
+        <v>3.070330524157812</v>
       </c>
       <c r="C1762" t="n">
         <v>3.010722978056604</v>
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336374</v>
+        <v>3.050895742336375</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42082,7 +42082,7 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320087</v>
+        <v>3.049222094320088</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477761</v>
+        <v>3.055423383477762</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.05975199725568</v>
+        <v>3.059751997255681</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227614</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.06824651857159</v>
+        <v>3.068246518571591</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408316</v>
+        <v>3.069025022408317</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708495</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968024</v>
+        <v>3.073923642968025</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066014</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293023</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239776</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.128298755003009</v>
+        <v>3.12829875500301</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167863</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216944</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.13201899645404</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780869</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.095206606537932</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.12341686637382</v>
+        <v>3.123416866373821</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502549</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.146730118728032</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702056</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487811</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.146265744823382</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524823</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068703</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714844</v>
+        <v>3.147014107714845</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083877</v>
+        <v>3.136752015083878</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666734</v>
+        <v>3.162269743666735</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097099</v>
+        <v>3.1634320910971</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762259</v>
+        <v>3.16927921276226</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.18551435596348</v>
+        <v>3.185514355963481</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583695</v>
+        <v>3.199276732583696</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742725</v>
+        <v>3.238767863742726</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589525</v>
+        <v>3.260068416589526</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872958</v>
+        <v>3.306739876872959</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.31216459594633</v>
+        <v>3.312164595946331</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336486</v>
+        <v>3.300520058336487</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308504</v>
+        <v>3.311781349308505</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257517</v>
+        <v>3.271427670257518</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,22 +43117,22 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.07597036178173</v>
+        <v>3.075970361781731</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>0.5654733158280743</v>
+        <v>0.5643896982427424</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.335087108738791</v>
+        <v>3.334653661704658</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.798788357339528</v>
+        <v>1.797704739754196</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.188527221125027</v>
+        <v>4.187877050573828</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231212.xlsx
+++ b/tame_output/ON/bt/strategyON_20231212.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -954,15 +954,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-366.7%</t>
+          <t>-383.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.0%</t>
+          <t>457.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-170.0%</t>
+          <t>-168.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-86.0%</t>
+          <t>-102.6%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,15 +1107,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-135.2%</t>
+          <t>-141.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-15.6%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-29.7%</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -42036,16 +42036,16 @@
         <v>45224</v>
       </c>
       <c r="B1762" t="n">
-        <v>3.070330524157812</v>
+        <v>3.070330524157811</v>
       </c>
       <c r="C1762" t="n">
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>-2.105030086592262</v>
+        <v>-2.269411039111522</v>
       </c>
       <c r="E1762" t="n">
-        <v>2.168354519105953</v>
+        <v>2.102602138098249</v>
       </c>
       <c r="F1762" t="n">
         <v>0.6676776475278887</v>
@@ -42059,16 +42059,16 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336375</v>
+        <v>3.050895742336374</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>-2.102677039259016</v>
+        <v>-2.267057991778277</v>
       </c>
       <c r="E1763" t="n">
-        <v>2.174635110176148</v>
+        <v>2.108882729168444</v>
       </c>
       <c r="F1763" t="n">
         <v>0.6700306948611342</v>
@@ -42082,16 +42082,16 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320088</v>
+        <v>3.049222094320087</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-2.10156075726779</v>
+        <v>-2.265941709787051</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.189658647808689</v>
+        <v>2.123906266800984</v>
       </c>
       <c r="F1764" t="n">
         <v>0.6711469768523604</v>
@@ -42111,10 +42111,10 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-2.097822801206735</v>
+        <v>-2.262203753725995</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.191078811096758</v>
+        <v>2.125326430089054</v>
       </c>
       <c r="F1765" t="n">
         <v>0.6735234291329851</v>
@@ -42128,16 +42128,16 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477762</v>
+        <v>3.055423383477761</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-2.089325655545602</v>
+        <v>-2.253706608064862</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.192793093859305</v>
+        <v>2.127040712851601</v>
       </c>
       <c r="F1766" t="n">
         <v>0.6735234291329851</v>
@@ -42157,10 +42157,10 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-2.089017695460877</v>
+        <v>-2.253398647980138</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.197304853574041</v>
+        <v>2.131552472566337</v>
       </c>
       <c r="F1767" t="n">
         <v>0.6747051432256852</v>
@@ -42174,16 +42174,16 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-2.087235933090286</v>
+        <v>-2.251616885609546</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.199677855699152</v>
+        <v>2.133925474691448</v>
       </c>
       <c r="F1768" t="n">
         <v>0.6747051432256852</v>
@@ -42197,16 +42197,16 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-2.091313288227377</v>
+        <v>-2.255694240746638</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.213081083908006</v>
+        <v>2.147328702900302</v>
       </c>
       <c r="F1769" t="n">
         <v>0.6747051432256852</v>
@@ -42220,16 +42220,16 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571591</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-2.081321207300968</v>
+        <v>-2.245702159820229</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.215392350942703</v>
+        <v>2.149639969934999</v>
       </c>
       <c r="F1770" t="n">
         <v>0.6846972241520943</v>
@@ -42243,16 +42243,16 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-2.081876962357006</v>
+        <v>-2.246257914876267</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.218071858816879</v>
+        <v>2.152319477809175</v>
       </c>
       <c r="F1771" t="n">
         <v>0.6830898103910163</v>
@@ -42266,16 +42266,16 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-2.085091314770318</v>
+        <v>-2.249472267289578</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.222311106990701</v>
+        <v>2.156558725982997</v>
       </c>
       <c r="F1772" t="n">
         <v>0.6830898103910163</v>
@@ -42289,16 +42289,16 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968025</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-2.102099560172927</v>
+        <v>-2.266480512692187</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.216585381467389</v>
+        <v>2.150833000459685</v>
       </c>
       <c r="F1773" t="n">
         <v>0.6860889454039901</v>
@@ -42312,16 +42312,16 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066014</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-2.083139837721573</v>
+        <v>-2.247520790240833</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.224919132619203</v>
+        <v>2.1591667516115</v>
       </c>
       <c r="F1774" t="n">
         <v>0.6860889454039901</v>
@@ -42335,16 +42335,16 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293023</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-2.081905113118764</v>
+        <v>-2.246286065638024</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.223648619923908</v>
+        <v>2.157896238916204</v>
       </c>
       <c r="F1775" t="n">
         <v>0.6860889454039901</v>
@@ -42358,16 +42358,16 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239776</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-2.091939376942413</v>
+        <v>-2.256320329461673</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.22320252423131</v>
+        <v>2.157450143223606</v>
       </c>
       <c r="F1776" t="n">
         <v>0.6860889454039901</v>
@@ -42381,16 +42381,16 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.12829875500301</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-2.09697837524028</v>
+        <v>-2.26135932775954</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.245168886801773</v>
+        <v>2.179416505794068</v>
       </c>
       <c r="F1777" t="n">
         <v>0.6810499471061233</v>
@@ -42404,16 +42404,16 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167863</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-2.087158657079729</v>
+        <v>-2.251539609598989</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.246565485553222</v>
+        <v>2.180813104545518</v>
       </c>
       <c r="F1778" t="n">
         <v>0.6874798873228107</v>
@@ -42427,16 +42427,16 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216944</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-2.085357030240775</v>
+        <v>-2.249737982760035</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.23253469829243</v>
+        <v>2.166782317284726</v>
       </c>
       <c r="F1779" t="n">
         <v>0.6874798873228107</v>
@@ -42450,16 +42450,16 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.13201899645404</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-2.084368348496607</v>
+        <v>-2.248749301015867</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.231043927305769</v>
+        <v>2.165291546298065</v>
       </c>
       <c r="F1780" t="n">
         <v>0.6874798873228107</v>
@@ -42473,16 +42473,16 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780869</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-2.076371993975068</v>
+        <v>-2.240752946494329</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.236216095570225</v>
+        <v>2.170463714562521</v>
       </c>
       <c r="F1781" t="n">
         <v>0.6954762418443493</v>
@@ -42496,16 +42496,16 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537932</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-2.07138824330316</v>
+        <v>-2.23576919582242</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.2500481764299</v>
+        <v>2.184295795422196</v>
       </c>
       <c r="F1782" t="n">
         <v>0.700459992516258</v>
@@ -42525,10 +42525,10 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-2.065002104353604</v>
+        <v>-2.229383056872865</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.259330835021511</v>
+        <v>2.193578454013807</v>
       </c>
       <c r="F1783" t="n">
         <v>0.700459992516258</v>
@@ -42548,10 +42548,10 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-2.076807454672237</v>
+        <v>-2.241188407191497</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.2586247836536</v>
+        <v>2.192872402645897</v>
       </c>
       <c r="F1784" t="n">
         <v>0.6886546421976254</v>
@@ -42571,10 +42571,10 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-2.068075643893571</v>
+        <v>-2.232456596412831</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.268064965574956</v>
+        <v>2.202312584567252</v>
       </c>
       <c r="F1785" t="n">
         <v>0.6973864529762916</v>
@@ -42588,16 +42588,16 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373821</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-2.061738757249119</v>
+        <v>-2.226119709768379</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.265910539180723</v>
+        <v>2.200158158173018</v>
       </c>
       <c r="F1786" t="n">
         <v>0.6973864529762916</v>
@@ -42611,16 +42611,16 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502549</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-2.05920430952175</v>
+        <v>-2.223585262041011</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.276886976073864</v>
+        <v>2.21113459506616</v>
       </c>
       <c r="F1787" t="n">
         <v>0.6973864529762916</v>
@@ -42634,16 +42634,16 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728032</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-2.059280208502355</v>
+        <v>-2.223661161021615</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.269271296674532</v>
+        <v>2.203518915666828</v>
       </c>
       <c r="F1788" t="n">
         <v>0.6981497136656185</v>
@@ -42657,16 +42657,16 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702056</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-2.069782398061701</v>
+        <v>-2.234163350580962</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.242834996641166</v>
+        <v>2.177082615633462</v>
       </c>
       <c r="F1789" t="n">
         <v>0.6876475241062718</v>
@@ -42680,16 +42680,16 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-2.071615660740818</v>
+        <v>-2.235996613260078</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.242802531415641</v>
+        <v>2.177050150407938</v>
       </c>
       <c r="F1790" t="n">
         <v>0.6876475241062718</v>
@@ -42703,16 +42703,16 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823382</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-2.076624775802402</v>
+        <v>-2.241005728321662</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.241315965219867</v>
+        <v>2.175563584212163</v>
       </c>
       <c r="F1791" t="n">
         <v>0.6866529465477371</v>
@@ -42726,16 +42726,16 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524823</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-2.080330332439216</v>
+        <v>-2.244711284958476</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.239061467805507</v>
+        <v>2.173309086797803</v>
       </c>
       <c r="F1792" t="n">
         <v>0.6847832712901022</v>
@@ -42749,16 +42749,16 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068703</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-2.079098007081851</v>
+        <v>-2.243478959601111</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.239974250010772</v>
+        <v>2.174221869003068</v>
       </c>
       <c r="F1793" t="n">
         <v>0.6854136476621397</v>
@@ -42772,16 +42772,16 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714845</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-2.068770010065998</v>
+        <v>-2.233150962585259</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.248235356981327</v>
+        <v>2.182482975973623</v>
       </c>
       <c r="F1794" t="n">
         <v>0.6957416446779919</v>
@@ -42795,16 +42795,16 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083878</v>
+        <v>3.136752015083877</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-2.068653674918443</v>
+        <v>-2.233034627437703</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.254802551242185</v>
+        <v>2.189050170234481</v>
       </c>
       <c r="F1795" t="n">
         <v>0.6958579798255476</v>
@@ -42818,16 +42818,16 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666735</v>
+        <v>3.162269743666734</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-2.07049908449531</v>
+        <v>-2.23488003701457</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.251038357856827</v>
+        <v>2.185285976849123</v>
       </c>
       <c r="F1796" t="n">
         <v>0.6958579798255476</v>
@@ -42841,16 +42841,16 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.1634320910971</v>
+        <v>3.163432091097099</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-2.069000651970211</v>
+        <v>-2.233381604489471</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.251576018728</v>
+        <v>2.185823637720296</v>
       </c>
       <c r="F1797" t="n">
         <v>0.6973564123506466</v>
@@ -42864,16 +42864,16 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.16927921276226</v>
+        <v>3.169279212762259</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-2.077064904162945</v>
+        <v>-2.241445856682205</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.249628295794218</v>
+        <v>2.183875914786514</v>
       </c>
       <c r="F1798" t="n">
         <v>0.6892921601579127</v>
@@ -42887,16 +42887,16 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963481</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-2.078394871624157</v>
+        <v>-2.242775824143417</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.249096308809733</v>
+        <v>2.183343927802029</v>
       </c>
       <c r="F1799" t="n">
         <v>0.6892921601579127</v>
@@ -42910,16 +42910,16 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583696</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-1.850530188890646</v>
+        <v>-2.014911141409907</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.3424586550103</v>
+        <v>2.276706274002596</v>
       </c>
       <c r="F1800" t="n">
         <v>0.6892921601579127</v>
@@ -42933,16 +42933,16 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742726</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-1.602428625023429</v>
+        <v>-1.76680957754269</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.449233876902279</v>
+        <v>2.383481495894574</v>
       </c>
       <c r="F1801" t="n">
         <v>0.6892921601579127</v>
@@ -42956,16 +42956,16 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589526</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-1.305590225630099</v>
+        <v>-1.469971178149359</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.569392247633068</v>
+        <v>2.503639866625364</v>
       </c>
       <c r="F1802" t="n">
         <v>0.8041466486390404</v>
@@ -42979,16 +42979,16 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872959</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-1.001950668804662</v>
+        <v>-1.166331621323923</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.69252514482893</v>
+        <v>2.626772763821225</v>
       </c>
       <c r="F1803" t="n">
         <v>0.8041466486390404</v>
@@ -43002,16 +43002,16 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946331</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-0.7129300623639536</v>
+        <v>-0.8773110148832144</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.80407280885467</v>
+        <v>2.738320427846966</v>
       </c>
       <c r="F1804" t="n">
         <v>0.8041466486390404</v>
@@ -43025,16 +43025,16 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336487</v>
+        <v>3.300520058336486</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-0.4282101351000565</v>
+        <v>-0.5925910876193172</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.923180919104247</v>
+        <v>2.857428538096543</v>
       </c>
       <c r="F1805" t="n">
         <v>1.088866575902938</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-0.1444484656085161</v>
+        <v>-0.3088294181277769</v>
       </c>
       <c r="E1806" t="n">
-        <v>3.04199775007467</v>
+        <v>2.976245369066966</v>
       </c>
       <c r="F1806" t="n">
         <v>1.088866575902938</v>
@@ -43071,16 +43071,16 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308505</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>0.1171999287841246</v>
+        <v>-0.04718102373513622</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.13989969527836</v>
+        <v>3.074147314270656</v>
       </c>
       <c r="F1807" t="n">
         <v>1.350514970295578</v>
@@ -43094,16 +43094,16 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257518</v>
+        <v>3.271427670257517</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>0.431366366923457</v>
+        <v>0.2669854144041962</v>
       </c>
       <c r="E1808" t="n">
-        <v>3.263029945550205</v>
+        <v>3.197277564542501</v>
       </c>
       <c r="F1808" t="n">
         <v>1.664681408434911</v>
@@ -43117,22 +43117,22 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.075970361781731</v>
+        <v>3.089567746659205</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>0.5643896982427424</v>
+        <v>0.3980515674636727</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.334653661704658</v>
+        <v>3.268118409393031</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.797704739754196</v>
+        <v>1.795747561494387</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.187877050573828</v>
+        <v>4.186702743617942</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231212.xlsx
+++ b/tame_output/ON/bt/strategyON_20231212.xlsx
@@ -934,12 +934,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-383.1%</t>
+          <t>-382.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.2%</t>
+          <t>457.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-168.2%</t>
+          <t>-168.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-141.8%</t>
+          <t>-141.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-30.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -42036,16 +42036,16 @@
         <v>45224</v>
       </c>
       <c r="B1762" t="n">
-        <v>3.070330524157811</v>
+        <v>3.070330524157812</v>
       </c>
       <c r="C1762" t="n">
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>-2.269411039111522</v>
+        <v>-2.260485543061785</v>
       </c>
       <c r="E1762" t="n">
-        <v>2.102602138098249</v>
+        <v>2.106172336518144</v>
       </c>
       <c r="F1762" t="n">
         <v>0.6676776475278887</v>
@@ -42059,16 +42059,16 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336374</v>
+        <v>3.050895742336375</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>-2.267057991778277</v>
+        <v>-2.25813249572854</v>
       </c>
       <c r="E1763" t="n">
-        <v>2.108882729168444</v>
+        <v>2.112452927588339</v>
       </c>
       <c r="F1763" t="n">
         <v>0.6700306948611342</v>
@@ -42082,16 +42082,16 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320087</v>
+        <v>3.049222094320088</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-2.265941709787051</v>
+        <v>-2.257016213737314</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.123906266800984</v>
+        <v>2.127476465220879</v>
       </c>
       <c r="F1764" t="n">
         <v>0.6711469768523604</v>
@@ -42111,10 +42111,10 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-2.262203753725995</v>
+        <v>-2.253278257676258</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.125326430089054</v>
+        <v>2.128896628508949</v>
       </c>
       <c r="F1765" t="n">
         <v>0.6735234291329851</v>
@@ -42128,16 +42128,16 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477761</v>
+        <v>3.055423383477762</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-2.253706608064862</v>
+        <v>-2.244781112015125</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.127040712851601</v>
+        <v>2.130610911271496</v>
       </c>
       <c r="F1766" t="n">
         <v>0.6735234291329851</v>
@@ -42157,10 +42157,10 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-2.253398647980138</v>
+        <v>-2.244473151930401</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.131552472566337</v>
+        <v>2.135122670986232</v>
       </c>
       <c r="F1767" t="n">
         <v>0.6747051432256852</v>
@@ -42180,10 +42180,10 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-2.251616885609546</v>
+        <v>-2.24269138955981</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.133925474691448</v>
+        <v>2.137495673111343</v>
       </c>
       <c r="F1768" t="n">
         <v>0.6747051432256852</v>
@@ -42203,10 +42203,10 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-2.255694240746638</v>
+        <v>-2.246768744696901</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.147328702900302</v>
+        <v>2.150898901320196</v>
       </c>
       <c r="F1769" t="n">
         <v>0.6747051432256852</v>
@@ -42226,10 +42226,10 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-2.245702159820229</v>
+        <v>-2.236776663770492</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.149639969934999</v>
+        <v>2.153210168354894</v>
       </c>
       <c r="F1770" t="n">
         <v>0.6846972241520943</v>
@@ -42249,10 +42249,10 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-2.246257914876267</v>
+        <v>-2.23733241882653</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.152319477809175</v>
+        <v>2.155889676229069</v>
       </c>
       <c r="F1771" t="n">
         <v>0.6830898103910163</v>
@@ -42272,10 +42272,10 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-2.249472267289578</v>
+        <v>-2.240546771239841</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.156558725982997</v>
+        <v>2.160128924402892</v>
       </c>
       <c r="F1772" t="n">
         <v>0.6830898103910163</v>
@@ -42295,10 +42295,10 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-2.266480512692187</v>
+        <v>-2.257555016642451</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.150833000459685</v>
+        <v>2.154403198879579</v>
       </c>
       <c r="F1773" t="n">
         <v>0.6860889454039901</v>
@@ -42312,16 +42312,16 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-2.247520790240833</v>
+        <v>-2.238595294191096</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.1591667516115</v>
+        <v>2.162736950031394</v>
       </c>
       <c r="F1774" t="n">
         <v>0.6860889454039901</v>
@@ -42335,16 +42335,16 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-2.246286065638024</v>
+        <v>-2.237360569588287</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.157896238916204</v>
+        <v>2.161466437336099</v>
       </c>
       <c r="F1775" t="n">
         <v>0.6860889454039901</v>
@@ -42358,16 +42358,16 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-2.256320329461673</v>
+        <v>-2.247394833411936</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.157450143223606</v>
+        <v>2.161020341643501</v>
       </c>
       <c r="F1776" t="n">
         <v>0.6860889454039901</v>
@@ -42387,10 +42387,10 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-2.26135932775954</v>
+        <v>-2.252433831709803</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.179416505794068</v>
+        <v>2.182986704213963</v>
       </c>
       <c r="F1777" t="n">
         <v>0.6810499471061233</v>
@@ -42404,16 +42404,16 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-2.251539609598989</v>
+        <v>-2.242614113549252</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.180813104545518</v>
+        <v>2.184383302965413</v>
       </c>
       <c r="F1778" t="n">
         <v>0.6874798873228107</v>
@@ -42427,16 +42427,16 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-2.249737982760035</v>
+        <v>-2.240812486710298</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.166782317284726</v>
+        <v>2.17035251570462</v>
       </c>
       <c r="F1779" t="n">
         <v>0.6874798873228107</v>
@@ -42450,16 +42450,16 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-2.248749301015867</v>
+        <v>-2.239823804966131</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.165291546298065</v>
+        <v>2.16886174471796</v>
       </c>
       <c r="F1780" t="n">
         <v>0.6874798873228107</v>
@@ -42473,16 +42473,16 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-2.240752946494329</v>
+        <v>-2.231827450444592</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.170463714562521</v>
+        <v>2.174033912982415</v>
       </c>
       <c r="F1781" t="n">
         <v>0.6954762418443493</v>
@@ -42496,16 +42496,16 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-2.23576919582242</v>
+        <v>-2.226843699772683</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.184295795422196</v>
+        <v>2.187865993842091</v>
       </c>
       <c r="F1782" t="n">
         <v>0.700459992516258</v>
@@ -42519,16 +42519,16 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-2.229383056872865</v>
+        <v>-2.220457560823128</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.193578454013807</v>
+        <v>2.197148652433702</v>
       </c>
       <c r="F1783" t="n">
         <v>0.700459992516258</v>
@@ -42542,16 +42542,16 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-2.241188407191497</v>
+        <v>-2.23226291114176</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.192872402645897</v>
+        <v>2.196442601065791</v>
       </c>
       <c r="F1784" t="n">
         <v>0.6886546421976254</v>
@@ -42565,16 +42565,16 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-2.232456596412831</v>
+        <v>-2.223531100363094</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.202312584567252</v>
+        <v>2.205882782987147</v>
       </c>
       <c r="F1785" t="n">
         <v>0.6973864529762916</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-2.226119709768379</v>
+        <v>-2.217194213718642</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.200158158173018</v>
+        <v>2.203728356592913</v>
       </c>
       <c r="F1786" t="n">
         <v>0.6973864529762916</v>
@@ -42611,16 +42611,16 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-2.223585262041011</v>
+        <v>-2.214659765991274</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.21113459506616</v>
+        <v>2.214704793486054</v>
       </c>
       <c r="F1787" t="n">
         <v>0.6973864529762916</v>
@@ -42634,16 +42634,16 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-2.223661161021615</v>
+        <v>-2.214735664971878</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.203518915666828</v>
+        <v>2.207089114086723</v>
       </c>
       <c r="F1788" t="n">
         <v>0.6981497136656185</v>
@@ -42657,16 +42657,16 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-2.234163350580962</v>
+        <v>-2.225237854531225</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.177082615633462</v>
+        <v>2.180652814053357</v>
       </c>
       <c r="F1789" t="n">
         <v>0.6876475241062718</v>
@@ -42680,16 +42680,16 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487809</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-2.235996613260078</v>
+        <v>-2.227071117210341</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.177050150407938</v>
+        <v>2.180620348827832</v>
       </c>
       <c r="F1790" t="n">
         <v>0.6876475241062718</v>
@@ -42703,16 +42703,16 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-2.241005728321662</v>
+        <v>-2.232080232271925</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.175563584212163</v>
+        <v>2.179133782632058</v>
       </c>
       <c r="F1791" t="n">
         <v>0.6866529465477371</v>
@@ -42726,16 +42726,16 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-2.244711284958476</v>
+        <v>-2.23578578890874</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.173309086797803</v>
+        <v>2.176879285217697</v>
       </c>
       <c r="F1792" t="n">
         <v>0.6847832712901022</v>
@@ -42749,16 +42749,16 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-2.243478959601111</v>
+        <v>-2.234553463551374</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.174221869003068</v>
+        <v>2.177792067422963</v>
       </c>
       <c r="F1793" t="n">
         <v>0.6854136476621397</v>
@@ -42772,16 +42772,16 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714844</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-2.233150962585259</v>
+        <v>-2.224225466535522</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.182482975973623</v>
+        <v>2.186053174393517</v>
       </c>
       <c r="F1794" t="n">
         <v>0.6957416446779919</v>
@@ -42795,16 +42795,16 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083877</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-2.233034627437703</v>
+        <v>-2.224109131387966</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.189050170234481</v>
+        <v>2.192620368654376</v>
       </c>
       <c r="F1795" t="n">
         <v>0.6958579798255476</v>
@@ -42818,16 +42818,16 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666734</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-2.23488003701457</v>
+        <v>-2.225954540964834</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.185285976849123</v>
+        <v>2.188856175269018</v>
       </c>
       <c r="F1796" t="n">
         <v>0.6958579798255476</v>
@@ -42841,16 +42841,16 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097099</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-2.233381604489471</v>
+        <v>-2.224456108439735</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.185823637720296</v>
+        <v>2.189393836140191</v>
       </c>
       <c r="F1797" t="n">
         <v>0.6973564123506466</v>
@@ -42864,16 +42864,16 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762259</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-2.241445856682205</v>
+        <v>-2.232520360632468</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.183875914786514</v>
+        <v>2.187446113206409</v>
       </c>
       <c r="F1798" t="n">
         <v>0.6892921601579127</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-2.242775824143417</v>
+        <v>-2.233850328093681</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.183343927802029</v>
+        <v>2.186914126221924</v>
       </c>
       <c r="F1799" t="n">
         <v>0.6892921601579127</v>
@@ -42910,16 +42910,16 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583695</v>
+        <v>3.199276732583694</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-2.014911141409907</v>
+        <v>-2.00598564536017</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.276706274002596</v>
+        <v>2.280276472422491</v>
       </c>
       <c r="F1800" t="n">
         <v>0.6892921601579127</v>
@@ -42933,16 +42933,16 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742725</v>
+        <v>3.238767863742724</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-1.76680957754269</v>
+        <v>-1.757884081492953</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.383481495894574</v>
+        <v>2.387051694314469</v>
       </c>
       <c r="F1801" t="n">
         <v>0.6892921601579127</v>
@@ -42956,16 +42956,16 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589525</v>
+        <v>3.260068416589524</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-1.469971178149359</v>
+        <v>-1.461045682099622</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.503639866625364</v>
+        <v>2.507210065045259</v>
       </c>
       <c r="F1802" t="n">
         <v>0.8041466486390404</v>
@@ -42979,16 +42979,16 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872958</v>
+        <v>3.306739876872957</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-1.166331621323923</v>
+        <v>-1.157406125274186</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.626772763821225</v>
+        <v>2.63034296224112</v>
       </c>
       <c r="F1803" t="n">
         <v>0.8041466486390404</v>
@@ -43002,16 +43002,16 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.31216459594633</v>
+        <v>3.312164595946329</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-0.8773110148832144</v>
+        <v>-0.8683855188334773</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.738320427846966</v>
+        <v>2.741890626266861</v>
       </c>
       <c r="F1804" t="n">
         <v>0.8041466486390404</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-0.5925910876193172</v>
+        <v>-0.5836655915695801</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.857428538096543</v>
+        <v>2.860998736516438</v>
       </c>
       <c r="F1805" t="n">
         <v>1.088866575902938</v>
@@ -43048,16 +43048,16 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.31844982914334</v>
+        <v>3.318449829143339</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-0.3088294181277769</v>
+        <v>-0.2999039220780397</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.976245369066966</v>
+        <v>2.97981556748686</v>
       </c>
       <c r="F1806" t="n">
         <v>1.088866575902938</v>
@@ -43071,16 +43071,16 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308504</v>
+        <v>3.311781349308503</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-0.04718102373513622</v>
+        <v>-0.03825552768539908</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.074147314270656</v>
+        <v>3.07771751269055</v>
       </c>
       <c r="F1807" t="n">
         <v>1.350514970295578</v>
@@ -43094,16 +43094,16 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257517</v>
+        <v>3.271427670257516</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>0.2669854144041962</v>
+        <v>0.2759109104539333</v>
       </c>
       <c r="E1808" t="n">
-        <v>3.197277564542501</v>
+        <v>3.200847762962396</v>
       </c>
       <c r="F1808" t="n">
         <v>1.664681408434911</v>
@@ -43117,22 +43117,22 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.089567746659205</v>
+        <v>3.089567746659204</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>0.3980515674636727</v>
+        <v>0.3984226145597057</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.268118409393031</v>
+        <v>3.268266828231444</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.795747561494387</v>
+        <v>1.787193112540683</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.186702743617942</v>
+        <v>4.18157007424572</v>
       </c>
     </row>
   </sheetData>
